--- a/artfynd/A 23496-2022 artfynd.xlsx
+++ b/artfynd/A 23496-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23496-2022 artfynd.xlsx
+++ b/artfynd/A 23496-2022 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>96738763</v>
       </c>
       <c r="B2" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734799.0146187339</v>
+        <v>734799</v>
       </c>
       <c r="R2" t="n">
-        <v>7056799.186538957</v>
+        <v>7056799</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,19 +748,9 @@
           <t>2021-10-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 23496-2022 artfynd.xlsx
+++ b/artfynd/A 23496-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,8 +783,16 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96738763</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 23496-2022 artfynd.xlsx
+++ b/artfynd/A 23496-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,53 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96738763</v>
+        <v>136102995</v>
       </c>
       <c r="B2" t="n">
-        <v>57132</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillån, Nordmaling, Ång</t>
+          <t>Lillån Sörbyn Hörnefors s:n, Ång, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734799</v>
+        <v>734787</v>
       </c>
       <c r="R2" t="n">
-        <v>7056799</v>
+        <v>7057062</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-19</t>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-19</t>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,20 +775,267 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136102995</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136102997</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lillån Sörbyn Hörnefors s:n, Ång, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>734772</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7057067</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>äldre ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136102997</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>96738763</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lillån, Nordmaling, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>734799</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7056799</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-10-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-10-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Carl Jansson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Carl Jansson, Henrik Sporrong</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/96738763</t>
         </is>
@@ -792,6 +1044,8 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23496-2022 artfynd.xlsx
+++ b/artfynd/A 23496-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136102995</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23496-2022 artfynd.xlsx
+++ b/artfynd/A 23496-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136102995</v>
       </c>
       <c r="B2" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136102997</v>
       </c>
       <c r="B3" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23496-2022 artfynd.xlsx
+++ b/artfynd/A 23496-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136102995</v>
       </c>
       <c r="B2" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136102997</v>
       </c>
       <c r="B3" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23496-2022 artfynd.xlsx
+++ b/artfynd/A 23496-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136102995</v>
       </c>
       <c r="B2" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136102997</v>
       </c>
       <c r="B3" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
